--- a/Documentation/EN/05 - Lab preparation v 2025-07-15 [EN].xlsx
+++ b/Documentation/EN/05 - Lab preparation v 2025-07-15 [EN].xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pohle/Dropbox/Central_Asia/Fluorometer/data/TJ_Zulmart/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pohle/Dropbox/Fribourg/2026/workshops/CA-hydroworkshop/materials/Documentation/EN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F507709-EA15-BF4E-99E0-9B5349A9F455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9BF063-FA51-2F4A-B3F6-4579F2A40644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="760" windowWidth="29060" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1180" yWindow="780" windowWidth="33400" windowHeight="21200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dilution concentration gravi" sheetId="6" r:id="rId1"/>
@@ -994,6 +994,51 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1005,51 +1050,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="8" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1543,44 +1543,44 @@
     <row r="10" spans="2:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75" t="s">
+      <c r="E10" s="90"/>
+      <c r="F10" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75" t="s">
+      <c r="G10" s="90"/>
+      <c r="H10" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="75"/>
-      <c r="J10" s="72" t="s">
+      <c r="I10" s="90"/>
+      <c r="J10" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="73"/>
-      <c r="L10" s="72" t="s">
+      <c r="K10" s="88"/>
+      <c r="L10" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="M10" s="73"/>
-      <c r="N10" s="72" t="s">
+      <c r="M10" s="88"/>
+      <c r="N10" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="O10" s="73"/>
-      <c r="P10" s="72" t="s">
+      <c r="O10" s="88"/>
+      <c r="P10" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="Q10" s="73"/>
-      <c r="R10" s="72" t="s">
+      <c r="Q10" s="88"/>
+      <c r="R10" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="S10" s="73"/>
+      <c r="S10" s="88"/>
     </row>
     <row r="11" spans="2:19" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="82" t="s">
+      <c r="B11" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="88" t="s">
+      <c r="C11" s="80" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="47" t="s">
@@ -1633,14 +1633,14 @@
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B12" s="83"/>
-      <c r="C12" s="89"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="81"/>
       <c r="D12" s="68">
         <f>E12/$F6</f>
-        <v>4.9697202729981731</v>
+        <v>1.9225223493223109</v>
       </c>
       <c r="E12" s="60">
-        <v>5.17</v>
+        <v>2</v>
       </c>
       <c r="F12" s="67">
         <f>G12</f>
@@ -1678,22 +1678,22 @@
       </c>
     </row>
     <row r="13" spans="2:19" ht="47" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="83"/>
+      <c r="B13" s="73"/>
       <c r="C13" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="90">
+      <c r="D13" s="82">
         <v>1000</v>
       </c>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90">
+      <c r="E13" s="82"/>
+      <c r="F13" s="82">
         <v>1000</v>
       </c>
-      <c r="G13" s="90"/>
-      <c r="H13" s="90">
+      <c r="G13" s="82"/>
+      <c r="H13" s="82">
         <v>1000</v>
       </c>
-      <c r="I13" s="90"/>
+      <c r="I13" s="82"/>
       <c r="J13" s="64">
         <f>J12*H17/1000*1000</f>
         <v>0</v>
@@ -1731,8 +1731,8 @@
       </c>
     </row>
     <row r="14" spans="2:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="B14" s="83"/>
-      <c r="C14" s="85" t="s">
+      <c r="B14" s="73"/>
+      <c r="C14" s="75" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="49" t="s">
@@ -1755,50 +1755,50 @@
       </c>
       <c r="J14" s="64">
         <f>K12*H17/1000*1000</f>
-        <v>20.700555920000003</v>
+        <v>8.0079520000000013</v>
       </c>
       <c r="K14" s="66" t="s">
         <v>32</v>
       </c>
       <c r="L14" s="65">
         <f>M12*H17/1000*1000</f>
-        <v>20.700555920000003</v>
+        <v>8.0079520000000013</v>
       </c>
       <c r="M14" s="66" t="s">
         <v>32</v>
       </c>
       <c r="N14" s="65">
         <f>O12*H17/1000*1000</f>
-        <v>20.700555920000003</v>
+        <v>8.0079520000000013</v>
       </c>
       <c r="O14" s="66" t="s">
         <v>32</v>
       </c>
       <c r="P14" s="65">
         <f>Q12*H17/1000*1000</f>
-        <v>25.875694900000003</v>
+        <v>10.009940000000002</v>
       </c>
       <c r="Q14" s="66" t="s">
         <v>32</v>
       </c>
       <c r="R14" s="65">
         <f>S12*H17/1000*1000</f>
-        <v>25.875694900000003</v>
+        <v>10.009940000000002</v>
       </c>
       <c r="S14" s="66" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B15" s="83"/>
-      <c r="C15" s="85"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="75"/>
       <c r="D15" s="51">
         <f>D12/D13</f>
-        <v>4.9697202729981731E-3</v>
+        <v>1.922522349322311E-3</v>
       </c>
       <c r="E15" s="52">
         <f>D12/D13</f>
-        <v>4.9697202729981731E-3</v>
+        <v>1.922522349322311E-3</v>
       </c>
       <c r="F15" s="51">
         <f>F12/F13</f>
@@ -1818,40 +1818,40 @@
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B16" s="83"/>
+      <c r="B16" s="73"/>
       <c r="C16" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="74">
+      <c r="D16" s="89">
         <f>E15*G15*I15</f>
-        <v>2.4798904162260886E-5</v>
-      </c>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
+        <v>9.5933865231183329E-6</v>
+      </c>
+      <c r="E16" s="89"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="89"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="89"/>
       <c r="L16" s="28"/>
       <c r="N16" s="28"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B17" s="83"/>
+      <c r="B17" s="73"/>
       <c r="C17" s="37" t="s">
         <v>0</v>
       </c>
       <c r="D17" s="76">
         <f>(E12*1000)/(D13*0.001)*(F5/1000)</f>
-        <v>518.55100000000004</v>
+        <v>200.6</v>
       </c>
       <c r="E17" s="76"/>
       <c r="F17" s="76">
         <f>D17*G15</f>
-        <v>2.5875694900000004</v>
+        <v>1.0009940000000002</v>
       </c>
       <c r="G17" s="76"/>
       <c r="H17" s="76">
         <f>F17*I15</f>
-        <v>2.5875694900000004</v>
+        <v>1.0009940000000002</v>
       </c>
       <c r="I17" s="76"/>
       <c r="J17" s="46"/>
@@ -1862,7 +1862,7 @@
       <c r="O17" s="31"/>
     </row>
     <row r="18" spans="2:15" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="83"/>
+      <c r="B18" s="73"/>
       <c r="C18" s="38" t="s">
         <v>14</v>
       </c>
@@ -1880,130 +1880,130 @@
       <c r="I18" s="77"/>
     </row>
     <row r="19" spans="2:15" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="83"/>
+      <c r="B19" s="73"/>
       <c r="C19" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="84" t="s">
+      <c r="D19" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84" t="s">
+      <c r="E19" s="74"/>
+      <c r="F19" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="84"/>
-      <c r="H19" s="84" t="s">
+      <c r="G19" s="74"/>
+      <c r="H19" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="84"/>
+      <c r="I19" s="74"/>
     </row>
     <row r="20" spans="2:15" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="83"/>
+      <c r="B20" s="73"/>
       <c r="C20" s="40" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
-      <c r="F20" s="79">
+      <c r="F20" s="84">
         <v>0.5</v>
       </c>
-      <c r="G20" s="79"/>
+      <c r="G20" s="84"/>
       <c r="H20" s="54"/>
       <c r="I20" s="54"/>
     </row>
     <row r="21" spans="2:15" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="83"/>
+      <c r="B21" s="73"/>
       <c r="C21" s="41" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="53"/>
       <c r="E21" s="53"/>
-      <c r="F21" s="80">
+      <c r="F21" s="85">
         <v>500</v>
       </c>
-      <c r="G21" s="80"/>
+      <c r="G21" s="85"/>
       <c r="H21" s="54"/>
       <c r="I21" s="54"/>
     </row>
     <row r="22" spans="2:15" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="83"/>
+      <c r="B22" s="73"/>
       <c r="C22" s="41" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
-      <c r="F22" s="81">
+      <c r="F22" s="86">
         <f>F20/F21</f>
         <v>1E-3</v>
       </c>
-      <c r="G22" s="81"/>
+      <c r="G22" s="86"/>
       <c r="H22" s="54"/>
       <c r="I22" s="54"/>
     </row>
     <row r="23" spans="2:15" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="83"/>
+      <c r="B23" s="73"/>
       <c r="C23" s="41" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="53"/>
       <c r="E23" s="53"/>
-      <c r="F23" s="81">
+      <c r="F23" s="86">
         <f>D16*F22</f>
-        <v>2.4798904162260886E-8</v>
-      </c>
-      <c r="G23" s="81"/>
+        <v>9.5933865231183327E-9</v>
+      </c>
+      <c r="G23" s="86"/>
       <c r="H23" s="54"/>
       <c r="I23" s="54"/>
     </row>
     <row r="24" spans="2:15" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="83"/>
+      <c r="B24" s="73"/>
       <c r="C24" s="42" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="53"/>
       <c r="E24" s="53"/>
-      <c r="F24" s="86">
+      <c r="F24" s="78">
         <f>F17*1000*F22</f>
-        <v>2.5875694900000004</v>
-      </c>
-      <c r="G24" s="86"/>
+        <v>1.0009940000000002</v>
+      </c>
+      <c r="G24" s="78"/>
       <c r="H24" s="54"/>
       <c r="I24" s="54"/>
     </row>
     <row r="25" spans="2:15" ht="81" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="83"/>
+      <c r="B25" s="73"/>
       <c r="C25" s="43" t="s">
         <v>5</v>
       </c>
       <c r="D25" s="53"/>
       <c r="E25" s="53"/>
-      <c r="F25" s="87" t="s">
+      <c r="F25" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="87"/>
+      <c r="G25" s="79"/>
       <c r="H25" s="54"/>
       <c r="I25" s="54"/>
     </row>
     <row r="26" spans="2:15" ht="81" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="83"/>
+      <c r="B26" s="73"/>
       <c r="C26" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="78">
+      <c r="D26" s="83">
         <f>D17*0.05*1000/5</f>
-        <v>5185.51</v>
-      </c>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78">
+        <v>2006.0000000000005</v>
+      </c>
+      <c r="E26" s="83"/>
+      <c r="F26" s="83">
         <f>F17*0.05*1000/5</f>
-        <v>25.875694900000006</v>
-      </c>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78">
+        <v>10.009940000000002</v>
+      </c>
+      <c r="G26" s="83"/>
+      <c r="H26" s="83">
         <f>H17*0.05*1000/5</f>
-        <v>25.875694900000006</v>
-      </c>
-      <c r="I26" s="78"/>
+        <v>10.009940000000002</v>
+      </c>
+      <c r="I26" s="83"/>
     </row>
     <row r="27" spans="2:15" ht="19" x14ac:dyDescent="0.25">
       <c r="J27" s="32" t="s">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="J28" s="33">
         <f>J14/(F7+K12/1000)</f>
-        <v>4.1334975878594253</v>
+        <v>1.5990319488817895</v>
       </c>
       <c r="K28" s="33"/>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="J29" s="33">
         <f>(J14+L14)/(F7+K12/1000+M12/1000)</f>
-        <v>8.2538101754385984</v>
+        <v>3.1929633173843706</v>
       </c>
       <c r="K29" s="33"/>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="J30" s="33">
         <f>(J14+L14+N14)/(F7+K12/1000+M12/1000+O12/1000)</f>
-        <v>12.361000748407646</v>
+        <v>4.78181847133758</v>
       </c>
       <c r="K30" s="33"/>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="J31" s="33">
         <f>(J14+L14+N14+P14)/(F7+K12/1000+M12/1000+O12/1000+Q12/1000)</f>
-        <v>17.476631438220107</v>
+        <v>6.7607858561779901</v>
       </c>
       <c r="K31" s="33"/>
     </row>
@@ -2066,13 +2066,30 @@
       </c>
       <c r="J32" s="33">
         <f>(J14+L14+N14+P14+R14)/(F7+K12/1000+M12/1000+O12/1000+Q12/1000+S12/1000)</f>
-        <v>22.571978104678831</v>
+        <v>8.7319064234734345</v>
       </c>
       <c r="K32" s="33"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <mergeCells count="33">
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
     <mergeCell ref="B11:B26"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="C14:C15"/>
@@ -2089,23 +2106,6 @@
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2408,15 +2408,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ddc3088f-455b-475b-8302-9f02570b14fd">
@@ -2425,6 +2416,15 @@
     <TaxCatchAll xmlns="6e7b6f15-1145-449f-a4bf-1f75763d2a97" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2663,20 +2663,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B052F2B8-7B0B-460A-86CE-BFB9676D95DD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FF71025-F80D-4439-9D0E-26A645E85F23}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ddc3088f-455b-475b-8302-9f02570b14fd"/>
     <ds:schemaRef ds:uri="6e7b6f15-1145-449f-a4bf-1f75763d2a97"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B052F2B8-7B0B-460A-86CE-BFB9676D95DD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
